--- a/config/bms/BCU_高特.xlsx
+++ b/config/bms/BCU_高特.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="386">
   <si>
     <t>序号</t>
   </si>
@@ -107,6 +107,9 @@
     <t>序号步长</t>
   </si>
   <si>
+    <t>告警等级</t>
+  </si>
+  <si>
     <t>组端过压 1 级报警</t>
   </si>
   <si>
@@ -116,19 +119,1075 @@
     <t>DiscreteInputs</t>
   </si>
   <si>
-    <t>电池组数</t>
+    <t>rackOvervoltageAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Overvoltage Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端过压 2 级报警</t>
+  </si>
+  <si>
+    <t>rackOvervoltageAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Overvoltage Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端过压 3 级报警</t>
+  </si>
+  <si>
+    <t>rackOvervoltageAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Overvoltage Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端欠压 1 级报警</t>
+  </si>
+  <si>
+    <t>rackUndervoltageAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Undervoltage Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端欠压 2 级报警</t>
+  </si>
+  <si>
+    <t>rackUndervoltageAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Undervoltage Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端欠压 3 级报警</t>
+  </si>
+  <si>
+    <t>rackUndervoltageAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Undervoltage Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端放电过流 1 级报警</t>
+  </si>
+  <si>
+    <t>rackDischargeOvercurrentAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Discharge Overcurrent Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端放电过流 2 级报警</t>
+  </si>
+  <si>
+    <t>rackDischargeOvercurrentAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Discharge Overcurrent Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端放电过流 3 级报警</t>
+  </si>
+  <si>
+    <t>rackDischargeOvercurrentAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Discharge Overcurrent Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端充电过流 1 级报警</t>
+  </si>
+  <si>
+    <t>rackChargeOvercurrentAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Charge Overcurrent Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端充电过流 2 级报警</t>
+  </si>
+  <si>
+    <t>rackChargeOvercurrentAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Charge Overcurrent Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端充电过流 3 级报警</t>
+  </si>
+  <si>
+    <t>rackChargeOvercurrentAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Charge Overcurrent Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端绝缘 1 级报警</t>
+  </si>
+  <si>
+    <t>rackInsulationAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Insulation Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端绝缘 2 级报警</t>
+  </si>
+  <si>
+    <t>rackInsulationAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Insulation Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端绝缘 3 级报警</t>
+  </si>
+  <si>
+    <t>rackInsulationAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Rack Insulation Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池充电过温 1 级报警</t>
+  </si>
+  <si>
+    <t>cellChargeOvertempAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Charge Overtemperature Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池充电过温 2 级报警</t>
+  </si>
+  <si>
+    <t>cellChargeOvertempAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Charge Overtemperature Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池充电过温 3 级报警</t>
+  </si>
+  <si>
+    <t>cellChargeOvertempAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Charge Overtemperature Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池充电欠温 1 级报警</t>
+  </si>
+  <si>
+    <t>cellChargeUndertempAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Charge Undertemperature Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池充电欠温 2 级报警</t>
+  </si>
+  <si>
+    <t>cellChargeUndertempAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Charge Undertemperature Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池充电欠温 3 级报警</t>
+  </si>
+  <si>
+    <t>cellChargeUndertempAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Charge Undertemperature Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电压过压 1 级报警</t>
+  </si>
+  <si>
+    <t>cellOvervoltageAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Overvoltage Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电压过压 2 级报警</t>
+  </si>
+  <si>
+    <t>cellOvervoltageAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Overvoltage Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电压过压 3 级报警</t>
+  </si>
+  <si>
+    <t>cellOvervoltageAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Overvoltage Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电压欠压 1 级报警</t>
+  </si>
+  <si>
+    <t>cellUndervoltageAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Undervoltage Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电压欠压 2 级报警</t>
+  </si>
+  <si>
+    <t>cellUndervoltageAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Undervoltage Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电压欠压 3 级报警</t>
+  </si>
+  <si>
+    <t>cellUndervoltageAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Undervoltage Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体压差过高 1 级报警</t>
+  </si>
+  <si>
+    <t>cellVoltageDiffAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Voltage Difference Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体压差过高 2 级报警</t>
+  </si>
+  <si>
+    <t>cellVoltageDiffAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Voltage Difference Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体压差过高 3 级报警</t>
+  </si>
+  <si>
+    <t>cellVoltageDiffAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Voltage Difference Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体温差过高 1 级报警</t>
+  </si>
+  <si>
+    <t>cellTempDiffAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Temperature Difference Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体温差过高 2 级报警</t>
+  </si>
+  <si>
+    <t>cellTempDiffAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Temperature Difference Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体温差过高 3 级报警</t>
+  </si>
+  <si>
+    <t>cellTempDiffAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Temperature Difference Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>SOC 过低 1 级告警</t>
+  </si>
+  <si>
+    <t>socLowAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Low SOC Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>SOC 过低 2 级告警</t>
+  </si>
+  <si>
+    <t>socLowAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Low SOC Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>SOC 过低 3 级告警</t>
+  </si>
+  <si>
+    <t>socLowAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Low SOC Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高 1 级报警</t>
+  </si>
+  <si>
+    <t>powerBoxOvertempAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Power Box Overtemperature Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高 2 级报警</t>
+  </si>
+  <si>
+    <t>powerBoxOvertempAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Power Box Overtemperature Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高 3 级报警</t>
+  </si>
+  <si>
+    <t>powerBoxOvertempAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Power Box Overtemperature Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>电池模组过压 1 级报警</t>
+  </si>
+  <si>
+    <t>moduleOvervoltageAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Module Overvoltage Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>电池模组过压 2 级报警</t>
+  </si>
+  <si>
+    <t>moduleOvervoltageAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Module Overvoltage Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>电池模组过压 3 级报警</t>
+  </si>
+  <si>
+    <t>moduleOvervoltageAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Module Overvoltage Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>电池模组欠压 1 级报警</t>
+  </si>
+  <si>
+    <t>moduleUndervoltageAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Module Undervoltage Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>电池模组欠压 2 级报警</t>
+  </si>
+  <si>
+    <t>moduleUndervoltageAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Module Undervoltage Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>电池模组欠压 3 级报警</t>
+  </si>
+  <si>
+    <t>moduleUndervoltageAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Module Undervoltage Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>DI1 故障</t>
+  </si>
+  <si>
+    <t>di1Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI1 Fault"}</t>
+  </si>
+  <si>
+    <t>DI2 故障</t>
+  </si>
+  <si>
+    <t>di2Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI2 Fault"}</t>
+  </si>
+  <si>
+    <t>DI3 故障</t>
+  </si>
+  <si>
+    <t>di3Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI3 Fault"}</t>
+  </si>
+  <si>
+    <t>DI4 故障</t>
+  </si>
+  <si>
+    <t>di4Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI4 Fault"}</t>
+  </si>
+  <si>
+    <t>DI5 故障</t>
+  </si>
+  <si>
+    <t>di5Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI5 Fault"}</t>
+  </si>
+  <si>
+    <t>DI6 故障</t>
+  </si>
+  <si>
+    <t>di6Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI6 Fault"}</t>
+  </si>
+  <si>
+    <t>DI7 故障</t>
+  </si>
+  <si>
+    <t>di7Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI7 Fault"}</t>
+  </si>
+  <si>
+    <t>DI8 故障</t>
+  </si>
+  <si>
+    <t>di8Fault</t>
+  </si>
+  <si>
+    <t>{"en": "DI8 Fault"}</t>
+  </si>
+  <si>
+    <t>内网通讯失联</t>
+  </si>
+  <si>
+    <t>internalCommLost</t>
+  </si>
+  <si>
+    <t>{"en": "Internal Network Communication Loss"}</t>
+  </si>
+  <si>
+    <t>单体电压采集异常</t>
+  </si>
+  <si>
+    <t>cellVoltageAcqFault</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Voltage Acquisition Fault"}</t>
+  </si>
+  <si>
+    <t>单体温度采集异常</t>
+  </si>
+  <si>
+    <t>cellTempAcqFault</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Temperature Acquisition Fault"}</t>
+  </si>
+  <si>
+    <t>显控检测故障</t>
+  </si>
+  <si>
+    <t>displayCtrlFault</t>
+  </si>
+  <si>
+    <t>{"en": "Display Controller Fault"}</t>
+  </si>
+  <si>
+    <t>簇间压差大</t>
+  </si>
+  <si>
+    <t>clusterVoltageDiffFault</t>
+  </si>
+  <si>
+    <t>{"en": "Inter-Cluster Voltage Difference Fault"}</t>
+  </si>
+  <si>
+    <t>簇间跳机故障</t>
+  </si>
+  <si>
+    <t>clusterTripFault</t>
+  </si>
+  <si>
+    <t>{"en": "Cluster Trip Fault"}</t>
+  </si>
+  <si>
+    <t>电池极限故障</t>
+  </si>
+  <si>
+    <t>batteryLimitFault</t>
+  </si>
+  <si>
+    <t>{"en": "Battery Limit Fault"}</t>
+  </si>
+  <si>
+    <t>项目软件版本参数不一致</t>
+  </si>
+  <si>
+    <t>projectVersionMismatch</t>
+  </si>
+  <si>
+    <t>{"en": "Project Software Version Mismatch"}</t>
+  </si>
+  <si>
+    <t>与 PCS 通讯故障</t>
+  </si>
+  <si>
+    <t>pcsCommFault</t>
+  </si>
+  <si>
+    <t>{"en": "PCS Communication Fault"}</t>
+  </si>
+  <si>
+    <t>PC 强控调试模式</t>
+  </si>
+  <si>
+    <t>pcForceDebugMode</t>
+  </si>
+  <si>
+    <t>{"en": "PC Forced Debug Mode"}</t>
+  </si>
+  <si>
+    <t>CAN 霍尔传感器故障</t>
+  </si>
+  <si>
+    <t>canHallSensorFault</t>
+  </si>
+  <si>
+    <t>{"en": "CAN Hall Sensor Fault"}</t>
+  </si>
+  <si>
+    <t>CAN 霍尔传感器通讯故障</t>
+  </si>
+  <si>
+    <t>canHallSensorCommFault</t>
+  </si>
+  <si>
+    <t>{"en": "CAN Hall Sensor Communication Fault"}</t>
+  </si>
+  <si>
+    <t>硬件自检异常</t>
+  </si>
+  <si>
+    <t>hardwareSelfCheckFault</t>
+  </si>
+  <si>
+    <t>{"en": "Hardware Self-Test Fault"}</t>
+  </si>
+  <si>
+    <t>单体电压线束故障</t>
+  </si>
+  <si>
+    <t>cellVoltageWiringFault</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Voltage Wiring Fault"}</t>
+  </si>
+  <si>
+    <t>均衡故障</t>
+  </si>
+  <si>
+    <t>balancingFault</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Balancing Fault"}</t>
+  </si>
+  <si>
+    <t>EMS 通讯故障</t>
+  </si>
+  <si>
+    <t>emsCommFault</t>
+  </si>
+  <si>
+    <t>{"en": "EMS Communication Fault"}</t>
+  </si>
+  <si>
+    <t>与三级 BMS 通讯故障</t>
+  </si>
+  <si>
+    <t>bms3CommFault</t>
+  </si>
+  <si>
+    <t>{"en": "Third-Level BMS Communication Fault"}</t>
+  </si>
+  <si>
+    <t>单体电池放电过温 1 级报警</t>
+  </si>
+  <si>
+    <t>cellDischargeOvertempAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Discharge Overtemperature Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池放电过温 2 级报警</t>
+  </si>
+  <si>
+    <t>cellDischargeOvertempAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Discharge Overtemperature Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池放电过温 3 级报警</t>
+  </si>
+  <si>
+    <t>cellDischargeOvertempAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Discharge Overtemperature Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池放电欠温 1 级报警</t>
+  </si>
+  <si>
+    <t>cellDischargeUndertempAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Discharge Undertemperature Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池放电欠温 2 级报警</t>
+  </si>
+  <si>
+    <t>cellDischargeUndertempAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Discharge Undertemperature Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>单体电池放电欠温 3 级报警</t>
+  </si>
+  <si>
+    <t>cellDischargeUndertempAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Cell Discharge Undertemperature Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>SOC 过高 1 级告警</t>
+  </si>
+  <si>
+    <t>socHighAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "High SOC Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>SOC 过高 2 级告警</t>
+  </si>
+  <si>
+    <t>socHighAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "High SOC Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>SOC 过高 3 级告警</t>
+  </si>
+  <si>
+    <t>socHighAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "High SOC Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>温升快报警 1 级报警</t>
+  </si>
+  <si>
+    <t>tempRiseFastAlarm1</t>
+  </si>
+  <si>
+    <t>{"en": "Rapid Temperature Rise Level 1 Alarm"}</t>
+  </si>
+  <si>
+    <t>温升快报警 2 级报警</t>
+  </si>
+  <si>
+    <t>tempRiseFastAlarm2</t>
+  </si>
+  <si>
+    <t>{"en": "Rapid Temperature Rise Level 2 Alarm"}</t>
+  </si>
+  <si>
+    <t>温升快报警 3 级报警</t>
+  </si>
+  <si>
+    <t>tempRiseFastAlarm3</t>
+  </si>
+  <si>
+    <t>{"en": "Rapid Temperature Rise Level 3 Alarm"}</t>
+  </si>
+  <si>
+    <t>组端过压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>HoldingRegisters</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>HoldingRegisters</t>
-  </si>
-  <si>
     <t>batteryGroupCount</t>
   </si>
   <si>
     <t>{"en":"Number of battery groups"}</t>
+  </si>
+  <si>
+    <t>组端过压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端过压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端过压报警回差值</t>
+  </si>
+  <si>
+    <t>组端欠压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端欠压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端欠压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端欠压报警回差值</t>
+  </si>
+  <si>
+    <t>组端放电过流 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>组端放电过流 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端放电过流 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端放电过流报警回差值</t>
+  </si>
+  <si>
+    <t>组端充电过流 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端充电过流 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端充电过流 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端充电过流报警回差值</t>
+  </si>
+  <si>
+    <t>组端绝缘 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>组端绝缘 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端绝缘 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>组端绝缘报警回差值</t>
+  </si>
+  <si>
+    <t>单体充电过温 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>单体充电过温 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体充电过温 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池充电过温报警回差值</t>
+  </si>
+  <si>
+    <t>单体充电欠温 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体充电欠温 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体充电欠温 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池充电欠温报警回差值</t>
+  </si>
+  <si>
+    <t>单体电压过压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压过压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压过压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压过压报警回差值</t>
+  </si>
+  <si>
+    <t>单体电压欠压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压欠压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压欠压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压欠压报警回差值</t>
+  </si>
+  <si>
+    <t>单体电压差压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压差压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压差压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体电压差压报警回差值</t>
+  </si>
+  <si>
+    <t>单体温度温差 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体温度温差 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体温度温差 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体温度温差报警回差值</t>
+  </si>
+  <si>
+    <t>SOC 过低 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>SOC 过低 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>SOC 过低 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>SOC 过低报警回差值</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>动力插箱温度过高报警回差值</t>
+  </si>
+  <si>
+    <t>电池模组过压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池模组过压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池模组过压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池模组过压报警回差值</t>
+  </si>
+  <si>
+    <t>电池模组欠压 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池模组欠压 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池模组欠压 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池模组欠压报警回差值</t>
+  </si>
+  <si>
+    <t>单体放电过温 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体放电过温 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体放电过温 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池放电过温报警回差值</t>
+  </si>
+  <si>
+    <t>单体放电欠温 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体放电欠温 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>单体放电欠温 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>电池放电欠温报警回差值</t>
+  </si>
+  <si>
+    <t>SOC 过高 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>SOC 过高 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>SOC 过高 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>SOC 过高报警回差值</t>
+  </si>
+  <si>
+    <t>温升快 1 级报警阈值</t>
+  </si>
+  <si>
+    <t>°C/min</t>
+  </si>
+  <si>
+    <t>温升快 2 级报警阈值</t>
+  </si>
+  <si>
+    <t>温升快 3 级报警阈值</t>
+  </si>
+  <si>
+    <t>温升快报警回差值</t>
+  </si>
+  <si>
+    <t>控制指令模式</t>
+  </si>
+  <si>
+    <t>上下电控制指令</t>
+  </si>
+  <si>
+    <t>DO 控制</t>
+  </si>
+  <si>
+    <t>风扇启动温度</t>
+  </si>
+  <si>
+    <t>风扇关闭温度</t>
+  </si>
+  <si>
+    <t>SOC/SOH 设置电池序号</t>
+  </si>
+  <si>
+    <t>SOC/SOH 设置</t>
+  </si>
+  <si>
+    <t>绝缘采集控制</t>
+  </si>
+  <si>
+    <t>可调风扇控制-占空比</t>
+  </si>
+  <si>
+    <t>复归指令</t>
+  </si>
+  <si>
+    <t>跳机指令</t>
+  </si>
+  <si>
+    <t>主控均衡控制(预留)</t>
+  </si>
+  <si>
+    <t>累计充电电量</t>
+  </si>
+  <si>
+    <t>累计放电电量</t>
+  </si>
+  <si>
+    <t>电池类型</t>
+  </si>
+  <si>
+    <t>电池容量</t>
+  </si>
+  <si>
+    <t>电传感器量程 1</t>
+  </si>
+  <si>
+    <t>电传感器量程 2</t>
+  </si>
+  <si>
+    <t>电传感器量程 3</t>
+  </si>
+  <si>
+    <t>簇内电池节数</t>
+  </si>
+  <si>
+    <t>簇内温度个数</t>
+  </si>
+  <si>
+    <t>簇内从控模块个数</t>
+  </si>
+  <si>
+    <t>从控 {n} 的电压个数</t>
+  </si>
+  <si>
+    <t>从控 {n} 的温度个数</t>
+  </si>
+  <si>
+    <t>从控站址自动分配</t>
+  </si>
+  <si>
+    <t>风扇控制功能</t>
   </si>
 </sst>
 </file>
@@ -141,7 +1200,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +1220,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -317,18 +1383,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -529,7 +1589,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -549,6 +1609,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -670,16 +1745,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -688,115 +1760,118 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -810,7 +1885,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -819,11 +1900,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -831,28 +1915,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1383,17 +2458,17 @@
   <dimension ref="A1:IV2"/>
   <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.03174603174603" style="3"/>
+    <col min="1" max="1" width="9.03174603174603" style="4"/>
     <col min="2" max="2" width="28.3571428571429" style="15" customWidth="1"/>
-    <col min="3" max="5" width="9.03174603174603" style="3"/>
-    <col min="6" max="6" width="10.1031746031746" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.3888888888889" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.03174603174603" style="3"/>
-    <col min="9" max="9" width="10.8412698412698" style="3" customWidth="1"/>
-    <col min="10" max="12" width="9.03174603174603" style="3"/>
-    <col min="13" max="13" width="31.984126984127" style="3" customWidth="1"/>
-    <col min="14" max="14" width="50.9206349206349" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9.03174603174603" style="3"/>
+    <col min="3" max="5" width="9.03174603174603" style="4"/>
+    <col min="6" max="6" width="10.1031746031746" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.3888888888889" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.03174603174603" style="4"/>
+    <col min="9" max="9" width="10.8412698412698" style="4" customWidth="1"/>
+    <col min="10" max="12" width="9.03174603174603" style="4"/>
+    <col min="13" max="13" width="31.984126984127" style="4" customWidth="1"/>
+    <col min="14" max="14" width="50.9206349206349" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.03174603174603" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:256">
@@ -1735,110 +2810,3200 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelRow="1"/>
+  <dimension ref="A1:T83"/>
+  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9.03174603174603" style="8"/>
-    <col min="2" max="2" width="48.5" style="9" customWidth="1"/>
-    <col min="3" max="6" width="9.03174603174603" style="8"/>
-    <col min="7" max="7" width="14.3809523809524" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9.03174603174603" style="8"/>
-    <col min="9" max="9" width="10.8412698412698" style="8" customWidth="1"/>
-    <col min="10" max="12" width="9.03174603174603" style="8"/>
-    <col min="13" max="13" width="3.11904761904762" style="8" customWidth="1"/>
-    <col min="14" max="14" width="11.968253968254" style="8" customWidth="1"/>
-    <col min="15" max="16384" width="9.03174603174603" style="8"/>
+    <col min="1" max="1" width="9.03174603174603" style="11"/>
+    <col min="2" max="2" width="48.5" style="12" customWidth="1"/>
+    <col min="3" max="6" width="9.03174603174603" style="11"/>
+    <col min="7" max="7" width="14.3809523809524" style="11" customWidth="1"/>
+    <col min="8" max="8" width="9.03174603174603" style="11"/>
+    <col min="9" max="9" width="10.8412698412698" style="11" customWidth="1"/>
+    <col min="10" max="12" width="9.03174603174603" style="11"/>
+    <col min="13" max="13" width="32.2301587301587" style="11" customWidth="1"/>
+    <col min="14" max="14" width="53.3095238095238" style="11" customWidth="1"/>
+    <col min="15" max="19" width="9.03174603174603" style="11"/>
+    <col min="20" max="20" width="12.4285714285714" style="11" customWidth="1"/>
+    <col min="21" max="16384" width="9.03174603174603" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:19">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:20">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" s="7" customFormat="1" spans="1:19">
-      <c r="A2" s="7">
-        <v>2000</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="T1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="12" t="s">
+    </row>
+    <row r="2" s="6" customFormat="1" spans="1:20">
+      <c r="A2" s="6">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="7">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="7">
-        <v>1</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="14"/>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="6">
+        <v>1</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="6">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6">
+        <v>5</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="T6" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="6">
+        <v>6</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="6">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6">
+        <v>8</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="T10" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="T11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="T12" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6">
+        <v>12</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="6">
+        <v>1</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T13" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="6">
+        <v>1</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="6">
+        <v>1013</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6">
+        <v>14</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="6">
+        <v>1014</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6">
+        <v>15</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="6">
+        <v>1</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="T16" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="6">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6">
+        <v>16</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="6">
+        <v>1016</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="6">
+        <v>17</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="6">
+        <v>1</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="T18" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" s="6">
+        <v>1017</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6">
+        <v>18</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="6">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="T19" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="6">
+        <v>1018</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6">
+        <v>19</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="6">
+        <v>1</v>
+      </c>
+      <c r="K20" s="6">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="T20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="6">
+        <v>1019</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="6">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1</v>
+      </c>
+      <c r="K21" s="6">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="T21" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" s="6">
+        <v>1020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6">
+        <v>21</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="6">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="6">
+        <v>1</v>
+      </c>
+      <c r="K22" s="6">
+        <v>0</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="T22" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" s="6">
+        <v>1021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="6">
+        <v>22</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="6">
+        <v>1</v>
+      </c>
+      <c r="K23" s="6">
+        <v>0</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="T23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" s="6">
+        <v>1022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="6">
+        <v>23</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="6">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="6">
+        <v>1</v>
+      </c>
+      <c r="K24" s="6">
+        <v>0</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="T24" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" s="6">
+        <v>1023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6">
+        <v>24</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="6">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1</v>
+      </c>
+      <c r="K25" s="6">
+        <v>0</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="T25" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="6">
+        <v>1024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="6">
+        <v>25</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="6">
+        <v>1</v>
+      </c>
+      <c r="K26" s="6">
+        <v>0</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="T26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" s="6">
+        <v>1025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="6">
+        <v>26</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="6">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="6">
+        <v>1</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T27" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28" s="6">
+        <v>1026</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="6">
+        <v>27</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H28" s="6">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="6">
+        <v>1</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="T28" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" s="6">
+        <v>1027</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="6">
+        <v>28</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="6">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="6">
+        <v>1</v>
+      </c>
+      <c r="K29" s="6">
+        <v>0</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="6">
+        <v>1028</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="6">
+        <v>29</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="6">
+        <v>1</v>
+      </c>
+      <c r="K30" s="6">
+        <v>0</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="T30" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="6">
+        <v>1029</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="6">
+        <v>30</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="6">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="6">
+        <v>1</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="T31" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32" s="6">
+        <v>1030</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="6">
+        <v>31</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="6">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="6">
+        <v>1</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="T32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" s="6">
+        <v>1031</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="6">
+        <v>32</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="6">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="6">
+        <v>1</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="T33" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" s="6">
+        <v>1032</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="6">
+        <v>33</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="6">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="6">
+        <v>1</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="T34" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" s="6">
+        <v>1033</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="6">
+        <v>34</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="6">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="6">
+        <v>1</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T35" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" s="6">
+        <v>1034</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="6">
+        <v>35</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="6">
+        <v>1</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="N36" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="T36" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" s="6">
+        <v>1035</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="6">
+        <v>36</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="6">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="6">
+        <v>1</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="N37" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="T37" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38" s="6">
+        <v>1036</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="6">
+        <v>37</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="6">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="6">
+        <v>1</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="N38" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="T38" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="A39" s="6">
+        <v>1037</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="6">
+        <v>38</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" s="6">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="6">
+        <v>1</v>
+      </c>
+      <c r="K39" s="6">
+        <v>0</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="N39" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="T39" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" s="6">
+        <v>1038</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="6">
+        <v>39</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="6">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="6">
+        <v>1</v>
+      </c>
+      <c r="K40" s="6">
+        <v>0</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="N40" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="T40" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="A41" s="6">
+        <v>1039</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="6">
+        <v>40</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41" s="6">
+        <v>1</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="6">
+        <v>1</v>
+      </c>
+      <c r="K41" s="6">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="N41" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="T41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42" s="6">
+        <v>1040</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="6">
+        <v>41</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="6">
+        <v>1</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="6">
+        <v>1</v>
+      </c>
+      <c r="K42" s="6">
+        <v>0</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="N42" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="T42" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" s="6">
+        <v>1041</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="6">
+        <v>42</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="6">
+        <v>1</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="6">
+        <v>1</v>
+      </c>
+      <c r="K43" s="6">
+        <v>0</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="T43" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" s="6">
+        <v>1042</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="6">
+        <v>43</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="6">
+        <v>1</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="6">
+        <v>1</v>
+      </c>
+      <c r="K44" s="6">
+        <v>0</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="N44" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="T44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45" s="6">
+        <v>1043</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="6">
+        <v>44</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="6">
+        <v>1</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="6">
+        <v>1</v>
+      </c>
+      <c r="K45" s="6">
+        <v>0</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N45" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="T45" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" s="6">
+        <v>1044</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="6">
+        <v>45</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H46" s="6">
+        <v>1</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="6">
+        <v>1</v>
+      </c>
+      <c r="K46" s="6">
+        <v>0</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="T46" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47" s="6">
+        <v>1045</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H47" s="6">
+        <v>1</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="6">
+        <v>1</v>
+      </c>
+      <c r="K47" s="6">
+        <v>0</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="N47" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="T47" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48" s="6">
+        <v>1046</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="6">
+        <v>47</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1</v>
+      </c>
+      <c r="K48" s="8">
+        <v>0</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="T48" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49" s="6">
+        <v>1047</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="6">
+        <v>48</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H49" s="8">
+        <v>1</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="8">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="N49" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="T49" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50" s="6">
+        <v>1048</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="6">
+        <v>49</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1</v>
+      </c>
+      <c r="K50" s="8">
+        <v>0</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="T50" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51" s="6">
+        <v>1049</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="6">
+        <v>50</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" s="8">
+        <v>1</v>
+      </c>
+      <c r="K51" s="8">
+        <v>0</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="T51" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52" s="6">
+        <v>1050</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="6">
+        <v>51</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H52" s="8">
+        <v>1</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" s="8">
+        <v>1</v>
+      </c>
+      <c r="K52" s="8">
+        <v>0</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="T52" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53" s="6">
+        <v>1051</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="6">
+        <v>52</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H53" s="8">
+        <v>1</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" s="8">
+        <v>1</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="T53" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54" s="6">
+        <v>1052</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="6">
+        <v>53</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1</v>
+      </c>
+      <c r="K54" s="8">
+        <v>0</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="T54" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55" s="6">
+        <v>1053</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="6">
+        <v>54</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H55" s="8">
+        <v>1</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" s="8">
+        <v>1</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="T55" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" s="6">
+        <v>1054</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="6">
+        <v>55</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H56" s="8">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="8">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8">
+        <v>0</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="N56" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="T56" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57" s="6">
+        <v>1055</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57" s="6">
+        <v>56</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H57" s="8">
+        <v>1</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="8">
+        <v>1</v>
+      </c>
+      <c r="K57" s="8">
+        <v>0</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="N57" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="T57" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58" s="6">
+        <v>1056</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="6">
+        <v>57</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H58" s="8">
+        <v>1</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" s="8">
+        <v>1</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="N58" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="T58" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" s="6">
+        <v>1057</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="6">
+        <v>58</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H59" s="8">
+        <v>1</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" s="8">
+        <v>1</v>
+      </c>
+      <c r="K59" s="8">
+        <v>0</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="N59" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="T59" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="A60" s="6">
+        <v>1058</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="6">
+        <v>59</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H60" s="8">
+        <v>1</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" s="8">
+        <v>1</v>
+      </c>
+      <c r="K60" s="8">
+        <v>0</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="N60" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="T60" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61" s="6">
+        <v>1059</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="6">
+        <v>60</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H61" s="8">
+        <v>1</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" s="8">
+        <v>1</v>
+      </c>
+      <c r="K61" s="8">
+        <v>0</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="T61" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62" s="6">
+        <v>1060</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="6">
+        <v>61</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H62" s="8">
+        <v>1</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="8">
+        <v>1</v>
+      </c>
+      <c r="K62" s="8">
+        <v>0</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="N62" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="T62" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
+      <c r="A63" s="6">
+        <v>1061</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="6">
+        <v>62</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H63" s="8">
+        <v>1</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="8">
+        <v>1</v>
+      </c>
+      <c r="K63" s="8">
+        <v>0</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="N63" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T63" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
+      <c r="A64" s="6">
+        <v>1062</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="6">
+        <v>63</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H64" s="8">
+        <v>1</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="8">
+        <v>1</v>
+      </c>
+      <c r="K64" s="8">
+        <v>0</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="N64" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="T64" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="6">
+        <v>1063</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="6">
+        <v>64</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="T65" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="6">
+        <v>1064</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="6">
+        <v>65</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="8">
+        <v>1</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="8">
+        <v>1</v>
+      </c>
+      <c r="K66" s="8">
+        <v>0</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="N66" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="T66" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" s="6">
+        <v>1065</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" s="6">
+        <v>66</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H67" s="8">
+        <v>1</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="8">
+        <v>1</v>
+      </c>
+      <c r="K67" s="8">
+        <v>0</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="N67" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="T67" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="6">
+        <v>1066</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="6">
+        <v>67</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H68" s="8">
+        <v>1</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="8">
+        <v>1</v>
+      </c>
+      <c r="K68" s="8">
+        <v>0</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="N68" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="T68" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="6">
+        <v>1067</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="6">
+        <v>68</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H69" s="8">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="8">
+        <v>1</v>
+      </c>
+      <c r="K69" s="8">
+        <v>0</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="N69" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="T69" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="6">
+        <v>1068</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="6">
+        <v>69</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H70" s="8">
+        <v>1</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" s="8">
+        <v>1</v>
+      </c>
+      <c r="K70" s="8">
+        <v>0</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="N70" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="T70" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71" s="6">
+        <v>1069</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="6">
+        <v>70</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H71" s="8">
+        <v>1</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="8">
+        <v>1</v>
+      </c>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="N71" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="T71" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72" s="6">
+        <v>1070</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="6">
+        <v>71</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H72" s="8">
+        <v>1</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="8">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8">
+        <v>0</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="N72" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="T72" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="6">
+        <v>1071</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="6">
+        <v>72</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H73" s="8">
+        <v>1</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="8">
+        <v>1</v>
+      </c>
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="N73" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="T73" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="A74" s="6">
+        <v>1072</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="6">
+        <v>73</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H74" s="8">
+        <v>1</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="8">
+        <v>1</v>
+      </c>
+      <c r="K74" s="8">
+        <v>0</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="N74" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="T74" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="A75" s="6">
+        <v>1073</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="6">
+        <v>74</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H75" s="8">
+        <v>1</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="8">
+        <v>1</v>
+      </c>
+      <c r="K75" s="8">
+        <v>0</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="N75" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="T75" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
+      <c r="A76" s="6">
+        <v>1074</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" s="6">
+        <v>75</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H76" s="8">
+        <v>1</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="8">
+        <v>1</v>
+      </c>
+      <c r="K76" s="8">
+        <v>0</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="N76" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="T76" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77" s="6">
+        <v>1075</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="6">
+        <v>76</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H77" s="8">
+        <v>1</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="8">
+        <v>1</v>
+      </c>
+      <c r="K77" s="8">
+        <v>0</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="N77" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="T77" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78" s="6">
+        <v>1076</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78" s="6">
+        <v>77</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H78" s="8">
+        <v>1</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="8">
+        <v>1</v>
+      </c>
+      <c r="K78" s="8">
+        <v>0</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="N78" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="T78" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79" s="6">
+        <v>1077</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79" s="6">
+        <v>78</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H79" s="8">
+        <v>1</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="8">
+        <v>1</v>
+      </c>
+      <c r="K79" s="8">
+        <v>0</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="N79" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="T79" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="A80" s="6">
+        <v>1078</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="6">
+        <v>79</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H80" s="8">
+        <v>1</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" s="8">
+        <v>1</v>
+      </c>
+      <c r="K80" s="8">
+        <v>0</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="N80" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="T80" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
+      <c r="A81" s="6">
+        <v>1079</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" s="6">
+        <v>80</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H81" s="8">
+        <v>1</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="8">
+        <v>1</v>
+      </c>
+      <c r="K81" s="8">
+        <v>0</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="N81" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="T81" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
+      <c r="A82" s="6">
+        <v>1080</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" s="6">
+        <v>81</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H82" s="8">
+        <v>1</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" s="8">
+        <v>1</v>
+      </c>
+      <c r="K82" s="8">
+        <v>0</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="N82" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="T82" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
+      <c r="A83" s="6">
+        <v>1081</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F83" s="6">
+        <v>82</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83" s="8">
+        <v>1</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="8">
+        <v>1</v>
+      </c>
+      <c r="K83" s="8">
+        <v>0</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="N83" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="T83" s="11">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1849,112 +6014,3217 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelRow="1"/>
+  <dimension ref="A1:S104"/>
+  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9.03174603174603" style="3"/>
-    <col min="2" max="2" width="17.6904761904762" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.30952380952381" style="3" customWidth="1"/>
-    <col min="4" max="6" width="9.03174603174603" style="3"/>
-    <col min="7" max="7" width="16.7222222222222" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.03174603174603" style="3"/>
-    <col min="9" max="9" width="10.8412698412698" style="3" customWidth="1"/>
-    <col min="10" max="12" width="9.03174603174603" style="3"/>
-    <col min="13" max="13" width="33.4365079365079" style="3" customWidth="1"/>
-    <col min="14" max="14" width="44.4285714285714" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9.03174603174603" style="3"/>
+    <col min="1" max="1" width="9.03174603174603" style="4"/>
+    <col min="2" max="2" width="29.0634920634921" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.30952380952381" style="4" customWidth="1"/>
+    <col min="4" max="6" width="9.03174603174603" style="4"/>
+    <col min="7" max="7" width="16.7222222222222" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.03174603174603" style="4"/>
+    <col min="9" max="9" width="10.8412698412698" style="4" customWidth="1"/>
+    <col min="10" max="12" width="9.03174603174603" style="4"/>
+    <col min="13" max="13" width="33.4365079365079" style="4" customWidth="1"/>
+    <col min="14" max="14" width="44.4285714285714" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.03174603174603" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" s="3" customFormat="1" spans="1:19">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="4">
-        <v>50000</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="6">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="6">
+        <v>2001</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="6">
+        <v>2002</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="6">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="6">
+        <v>2003</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="6">
+        <v>2004</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F6" s="6">
+        <v>5</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="6">
+        <v>2005</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F7" s="6">
+        <v>6</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="6">
+        <v>2006</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F8" s="6">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="6">
+        <v>2007</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F9" s="6">
+        <v>8</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="6">
+        <v>2008</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F10" s="6">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="6">
+        <v>2009</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="6">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="6">
+        <v>2010</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F12" s="6">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="6">
+        <v>2011</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13" s="6">
+        <v>12</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="6">
+        <v>2012</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F14" s="6">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="6">
+        <v>2013</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15" s="6">
+        <v>14</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="6">
+        <v>2014</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16" s="6">
+        <v>15</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="6">
+        <v>2015</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F17" s="6">
+        <v>16</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="6">
+        <v>2016</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F18" s="6">
+        <v>17</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="6">
+        <v>2017</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F19" s="6">
+        <v>18</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="6">
+        <v>2018</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F20" s="6">
+        <v>19</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="K20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="6">
+        <v>2019</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F21" s="6">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="4">
+        <v>1</v>
+      </c>
+      <c r="K21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="6">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F22" s="6">
+        <v>21</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H22" s="6">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="6">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F23" s="6">
+        <v>22</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K23" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F24" s="6">
+        <v>23</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="6">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K24" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="6">
+        <v>24</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H25" s="6">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F26" s="6">
+        <v>25</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K26" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F27" s="6">
+        <v>26</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H27" s="6">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K27" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F28" s="6">
+        <v>27</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H28" s="6">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K28" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="6">
+        <v>2027</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F29" s="6">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="G29" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H29" s="6">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="6">
+        <v>2028</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F30" s="6">
         <v>29</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="4">
-        <v>500</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="G30" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0.001</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="6">
+        <v>2029</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F31" s="6">
         <v>30</v>
       </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="G31" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="6">
+        <v>2030</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" s="6">
         <v>31</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="G32" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H32" s="8">
+        <v>1</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="6">
+        <v>2031</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F33" s="6">
         <v>32</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="6">
+        <v>2032</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F34" s="6">
+        <v>33</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H34" s="8">
+        <v>1</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="6">
+        <v>2033</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F35" s="6">
+        <v>34</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H35" s="8">
+        <v>1</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="6">
+        <v>2034</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F36" s="6">
+        <v>35</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H36" s="8">
+        <v>1</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K36" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="6">
+        <v>2035</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F37" s="6">
+        <v>36</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H37" s="8">
+        <v>1</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="6">
+        <v>2036</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="6">
+        <v>37</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H38" s="8">
+        <v>1</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K38" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="6">
+        <v>2037</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F39" s="6">
+        <v>38</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H39" s="8">
+        <v>1</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K39" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="6">
+        <v>2038</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F40" s="6">
+        <v>39</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H40" s="8">
+        <v>1</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K40" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="6">
+        <v>2039</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F41" s="6">
+        <v>40</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H41" s="8">
+        <v>1</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="K41" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="6">
+        <v>2040</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F42" s="6">
+        <v>41</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H42" s="8">
+        <v>1</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="K42" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="6">
+        <v>2041</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F43" s="6">
+        <v>42</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H43" s="8">
+        <v>1</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="K43" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="6">
+        <v>2042</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F44" s="6">
+        <v>43</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H44" s="8">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="K44" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="6">
+        <v>2043</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F45" s="6">
+        <v>44</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H45" s="8">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K45" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="6">
+        <v>2044</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F46" s="6">
+        <v>45</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H46" s="8">
+        <v>1</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1</v>
+      </c>
+      <c r="K46" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="6">
+        <v>2045</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H47" s="8">
+        <v>1</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="8">
+        <v>1</v>
+      </c>
+      <c r="K47" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="6">
+        <v>2046</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F48" s="6">
+        <v>47</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1</v>
+      </c>
+      <c r="K48" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="6">
+        <v>2047</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F49" s="6">
+        <v>48</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H49" s="8">
+        <v>1</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="8">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="6">
+        <v>2048</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F50" s="6">
+        <v>49</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K50" s="8">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="6">
+        <v>2049</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F51" s="6">
+        <v>50</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K51" s="8">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="6">
+        <v>2050</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="6">
+        <v>51</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H52" s="8">
+        <v>1</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K52" s="8">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="6">
+        <v>2051</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F53" s="6">
+        <v>52</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H53" s="8">
+        <v>1</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="6">
+        <v>2052</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F54" s="6">
+        <v>53</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K54" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="6">
+        <v>2053</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F55" s="6">
+        <v>54</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H55" s="8">
+        <v>1</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="6">
+        <v>2054</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F56" s="6">
+        <v>55</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H56" s="8">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K56" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="6">
+        <v>2055</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F57" s="6">
+        <v>56</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H57" s="8">
+        <v>1</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K57" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="6">
+        <v>2056</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F58" s="6">
+        <v>57</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H58" s="8">
+        <v>1</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="6">
+        <v>2057</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F59" s="6">
+        <v>58</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H59" s="8">
+        <v>1</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K59" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="6">
+        <v>2058</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F60" s="6">
+        <v>59</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H60" s="8">
+        <v>1</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K60" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="6">
+        <v>2059</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F61" s="6">
+        <v>60</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H61" s="8">
+        <v>1</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K61" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="6">
+        <v>2060</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F62" s="6">
+        <v>61</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H62" s="9">
+        <v>1</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K62" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="6">
+        <v>2061</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F63" s="6">
+        <v>62</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H63" s="9">
+        <v>1</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K63" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="6">
+        <v>2062</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F64" s="6">
+        <v>63</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H64" s="9">
+        <v>1</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K64" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="6">
+        <v>2063</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F65" s="6">
+        <v>64</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="6">
+        <v>2064</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F66" s="6">
+        <v>65</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H66" s="9">
+        <v>1</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K66" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="6">
+        <v>2065</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F67" s="6">
+        <v>66</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H67" s="9">
+        <v>1</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K67" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="6">
+        <v>2066</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F68" s="6">
+        <v>67</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H68" s="9">
+        <v>1</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K68" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="6">
+        <v>2067</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F69" s="6">
+        <v>68</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H69" s="8">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="K69" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="6">
+        <v>2068</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F70" s="6">
+        <v>69</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H70" s="8">
+        <v>1</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" s="9">
+        <v>1</v>
+      </c>
+      <c r="K70" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="6">
+        <v>2069</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F71" s="6">
+        <v>70</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H71" s="8">
+        <v>1</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="9">
+        <v>1</v>
+      </c>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="6">
+        <v>2070</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F72" s="6">
+        <v>71</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H72" s="8">
+        <v>1</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="9">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="6">
+        <v>2071</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F73" s="6">
+        <v>72</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H73" s="8">
+        <v>1</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="9">
+        <v>1</v>
+      </c>
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="6">
+        <v>2072</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" s="6">
+        <v>73</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H74" s="8">
+        <v>1</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="9">
+        <v>1</v>
+      </c>
+      <c r="K74" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="6">
+        <v>2073</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F75" s="6">
+        <v>74</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H75" s="8">
+        <v>1</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="9">
+        <v>1</v>
+      </c>
+      <c r="K75" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="6">
+        <v>2074</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F76" s="6">
+        <v>75</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H76" s="8">
+        <v>1</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="9">
+        <v>1</v>
+      </c>
+      <c r="K76" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="6">
+        <v>2075</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F77" s="6">
+        <v>76</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H77" s="8">
+        <v>1</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="9">
+        <v>1</v>
+      </c>
+      <c r="K77" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="B78" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="4">
+        <v>99</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H78" s="8">
+        <v>1</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="9">
+        <v>1</v>
+      </c>
+      <c r="K78" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="B79" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="4">
+        <v>100</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H79" s="8">
+        <v>1</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="9">
+        <v>1</v>
+      </c>
+      <c r="K79" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="B80" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="4">
+        <v>101</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H80" s="8">
+        <v>1</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" s="9">
+        <v>1</v>
+      </c>
+      <c r="K80" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="4">
+        <v>102</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H81" s="8">
+        <v>1</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="9">
+        <v>1</v>
+      </c>
+      <c r="K81" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="4">
+        <v>103</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H82" s="8">
+        <v>1</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" s="9">
+        <v>1</v>
+      </c>
+      <c r="K82" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="4">
+        <v>104</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H83" s="8">
+        <v>1</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="9">
+        <v>1</v>
+      </c>
+      <c r="K83" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="4">
+        <v>105</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H84" s="8">
+        <v>1</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" s="9">
+        <v>1</v>
+      </c>
+      <c r="K84" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" s="4">
+        <v>106</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" s="8">
+        <v>1</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" s="9">
+        <v>1</v>
+      </c>
+      <c r="K85" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="4">
+        <v>107</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H86" s="8">
+        <v>1</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" s="9">
+        <v>1</v>
+      </c>
+      <c r="K86" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="4">
+        <v>108</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H87" s="8">
+        <v>1</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J87" s="9">
+        <v>1</v>
+      </c>
+      <c r="K87" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="4">
+        <v>109</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H88" s="8">
+        <v>1</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" s="9">
+        <v>1</v>
+      </c>
+      <c r="K88" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="4">
+        <v>110</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H89" s="8">
+        <v>1</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" s="9">
+        <v>1</v>
+      </c>
+      <c r="K89" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="4">
+        <v>111</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H90" s="8">
+        <v>1</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J90" s="9">
+        <v>1</v>
+      </c>
+      <c r="K90" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="4">
+        <v>112</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H91" s="8">
+        <v>1</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" s="9">
+        <v>1</v>
+      </c>
+      <c r="K91" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="4">
+        <v>114</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H92" s="8">
+        <v>1</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" s="9">
+        <v>1</v>
+      </c>
+      <c r="K92" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="4">
+        <v>116</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H93" s="8">
+        <v>1</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J93" s="9">
+        <v>1</v>
+      </c>
+      <c r="K93" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="4">
+        <v>117</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H94" s="8">
+        <v>1</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" s="9">
+        <v>1</v>
+      </c>
+      <c r="K94" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="4">
+        <v>118</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H95" s="8">
+        <v>1</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" s="9">
+        <v>1</v>
+      </c>
+      <c r="K95" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="4">
+        <v>119</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H96" s="8">
+        <v>1</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" s="9">
+        <v>1</v>
+      </c>
+      <c r="K96" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="4">
+        <v>120</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H97" s="8">
+        <v>1</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" s="9">
+        <v>1</v>
+      </c>
+      <c r="K97" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="4">
+        <v>121</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H98" s="8">
+        <v>1</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J98" s="9">
+        <v>1</v>
+      </c>
+      <c r="K98" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="4">
+        <v>122</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H99" s="8">
+        <v>1</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J99" s="9">
+        <v>1</v>
+      </c>
+      <c r="K99" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="B100" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="4">
+        <v>123</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H100" s="8">
+        <v>1</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J100" s="9">
+        <v>1</v>
+      </c>
+      <c r="K100" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="4">
+        <v>124</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H101" s="8">
+        <v>1</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="9">
+        <v>1</v>
+      </c>
+      <c r="K101" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102" s="4">
+        <v>172</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H102" s="8">
+        <v>1</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" s="9">
+        <v>1</v>
+      </c>
+      <c r="K102" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" s="4">
+        <v>220</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H103" s="8">
+        <v>1</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J103" s="9">
+        <v>1</v>
+      </c>
+      <c r="K103" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="4">
+        <v>221</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H104" s="8">
+        <v>1</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" s="9">
+        <v>1</v>
+      </c>
+      <c r="K104" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
